--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104548_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104548_W10.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5172</v>
+        <v>2.5908</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0965</v>
+        <v>0.8554</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4207</v>
+        <v>1.7354</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1096</v>
+        <v>2.1171</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3637</v>
+        <v>0.362</v>
       </c>
       <c r="I2" t="n">
-        <v>1.746</v>
+        <v>1.7552</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0226</v>
+        <v>3.0047</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8285</v>
+        <v>1.8131</v>
       </c>
       <c r="L2" t="n">
-        <v>1.1941</v>
+        <v>1.1916</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.913</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8193</v>
+        <v>-0.7539</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4083</v>
+        <v>0.1969</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2276</v>
+        <v>-0.9509</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6645</v>
+        <v>1.3818</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4513</v>
+        <v>2.2555</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.8737</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5624</v>
+        <v>0.5515</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3621</v>
+        <v>-1.3668</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9245</v>
+        <v>1.9184</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2266</v>
+        <v>2.185</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4809</v>
+        <v>0.4579</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7458</v>
+        <v>1.7271</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6643</v>
+        <v>-1.6335</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8429</v>
+        <v>-1.8248</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6199</v>
+        <v>-0.9013</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3217</v>
+        <v>-0.4743</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2982</v>
+        <v>-0.427</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3421</v>
+        <v>0.6424</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3082</v>
+        <v>0.3629</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0338</v>
+        <v>0.2795</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.418</v>
+        <v>-0.4108</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7778</v>
+        <v>-0.7729</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3599</v>
+        <v>0.3621</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6314</v>
+        <v>0.619</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3361</v>
+        <v>-0.3415</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0494</v>
+        <v>-1.0298</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0546</v>
+        <v>-0.7678</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2571</v>
+        <v>-0.1862</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7976</v>
+        <v>-0.5816</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1129</v>
+        <v>0.0375</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9204</v>
+        <v>1.1522</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0333</v>
+        <v>-1.1147</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4265</v>
+        <v>0.4325</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3492</v>
+        <v>0.3503</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.111</v>
+        <v>1.1059</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0736</v>
+        <v>1.0687</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6844</v>
+        <v>-0.6734</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2199</v>
+        <v>-0.0779</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1905</v>
+        <v>0.0463</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0293</v>
+        <v>-0.1242</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5326</v>
+        <v>-1.0002</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.347</v>
+        <v>-1.6443</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8144</v>
+        <v>0.6442</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2285</v>
+        <v>-1.2246</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.834</v>
+        <v>-0.833</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3945</v>
+        <v>-0.3916</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6696</v>
+        <v>-0.6802</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5444</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0835</v>
+        <v>-0.3902</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4567</v>
+        <v>0.174</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3732</v>
+        <v>-0.5642</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>G. KNUDSEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.865</v>
+        <v>-2.9479</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0054</v>
+        <v>-3.1196</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8596</v>
+        <v>0.1718</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.9876</v>
+        <v>-3.7514</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1328</v>
+        <v>-2.3633</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.8548</v>
+        <v>-1.3881</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.8674</v>
+        <v>-2.2623</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1661</v>
+        <v>-1.4726</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.0335</v>
+        <v>-0.7896</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1202</v>
+        <v>-1.4891</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.2989</v>
+        <v>-0.8907</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1787</v>
+        <v>-0.5984</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4421</v>
+        <v>0.1206</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9962</v>
+        <v>0.5084</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5541</v>
+        <v>-0.3878</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. KNUDSEN</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.547</v>
+        <v>-3.9502</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.7602</v>
+        <v>-3.1839</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2132</v>
+        <v>-0.7663</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.7503</v>
+        <v>-4.9814</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.3562</v>
+        <v>-2.1257</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.394</v>
+        <v>-2.8556</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.245</v>
+        <v>-2.8885</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4586</v>
+        <v>0.1584</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7864</v>
+        <v>-3.0469</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5053</v>
+        <v>-2.0929</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8976</v>
+        <v>-2.2841</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6077</v>
+        <v>0.1912</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4773</v>
+        <v>0.3483</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1542</v>
+        <v>0.8428</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.323</v>
+        <v>-0.4945</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4184</v>
+        <v>-4.36</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.6281</v>
+        <v>-4.5343</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2097</v>
+        <v>0.1743</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.1165</v>
+        <v>-4.1346</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.2476</v>
+        <v>-3.2755</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8689</v>
+        <v>-0.8591</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0331</v>
+        <v>-2.0718</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.1451</v>
+        <v>-2.1835</v>
       </c>
       <c r="L9" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0834</v>
+        <v>-2.0628</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.075</v>
+        <v>0.0022</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0998</v>
+        <v>0.0414</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0248</v>
+        <v>-0.0392</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2813</v>
+        <v>-5.0594</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3156</v>
+        <v>-3.1394</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9657</v>
+        <v>-1.9201</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0421</v>
+        <v>-3.0396</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6667</v>
+        <v>-1.6631</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3754</v>
+        <v>-1.3765</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5554</v>
+        <v>-1.562</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4867</v>
+        <v>-1.4775</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6929</v>
+        <v>-0.4751</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3992</v>
+        <v>-0.2115</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2937</v>
+        <v>-0.2636</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7186</v>
+        <v>-5.2954</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2297</v>
+        <v>-2.8415</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4889</v>
+        <v>-2.4539</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4041</v>
+        <v>-2.4046</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9349</v>
+        <v>-1.9385</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4691</v>
+        <v>-0.4661</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3716</v>
+        <v>-0.3999</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6274</v>
+        <v>-0.6452</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0325</v>
+        <v>-2.0047</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.995</v>
+        <v>-0.5737</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5898</v>
+        <v>-0.1652</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4053</v>
+        <v>-0.4085</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.289899999999999</v>
+        <v>-8.2357</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9593</v>
+        <v>-5.8772</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3307</v>
+        <v>-2.3585</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7282</v>
+        <v>-3.735</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.3662</v>
+        <v>-2.3829</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.362</v>
+        <v>-1.3521</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1921</v>
+        <v>-1.2277</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.555</v>
+        <v>-0.587</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5361</v>
+        <v>-2.5073</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8112</v>
+        <v>-1.7959</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.083</v>
+        <v>-4.0974</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0931</v>
+        <v>-0.0163</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1966</v>
+        <v>0.3388</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2898</v>
+        <v>-0.3551</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-27.2419</v>
+        <v>-26.1963</v>
       </c>
       <c r="E13" t="n">
-        <v>-20.4689</v>
+        <v>-19.7142</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.7732</v>
+        <v>-6.481999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-20.5768</v>
+        <v>-20.5809</v>
       </c>
       <c r="H13" t="n">
-        <v>-15.9654</v>
+        <v>-16.0094</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.611</v>
+        <v>-4.571299999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.9426</v>
+        <v>-4.177800000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.2626</v>
+        <v>-2.4319</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.6799</v>
+        <v>-1.7458</v>
       </c>
       <c r="M13" t="n">
-        <v>-16.6343</v>
+        <v>-16.403</v>
       </c>
       <c r="N13" t="n">
-        <v>-13.7028</v>
+        <v>-13.5775</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.9312</v>
+        <v>-2.8255</v>
       </c>
       <c r="P13" t="n">
-        <v>1.134099999999998</v>
+        <v>1.138099999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-18.1467</v>
+        <v>-18.2105</v>
       </c>
       <c r="R13" t="n">
-        <v>19.2807</v>
+        <v>19.3486</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.5214</v>
+        <v>-3.4851</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04549999999999987</v>
+        <v>1.1114</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.566999999999999</v>
+        <v>-4.5966</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5748</v>
+        <v>1.5628</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.8529</v>
+        <v>-4.8312</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.1914</v>
+        <v>7.9399</v>
       </c>
       <c r="E14" t="n">
-        <v>7.3402</v>
+        <v>6.959</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8512</v>
+        <v>0.9809</v>
       </c>
       <c r="G14" t="n">
-        <v>5.8853</v>
+        <v>5.8934</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0012</v>
+        <v>3.0095</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8841</v>
+        <v>2.8839</v>
       </c>
       <c r="J14" t="n">
-        <v>6.6619</v>
+        <v>6.6387</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6019</v>
+        <v>3.5853</v>
       </c>
       <c r="L14" t="n">
-        <v>3.06</v>
+        <v>3.0534</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7765</v>
+        <v>-0.7453</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6007</v>
+        <v>-0.5758</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9866</v>
+        <v>0.7294</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9467</v>
+        <v>0.5966</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0399</v>
+        <v>0.1328</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9731</v>
+        <v>7.2563</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1739</v>
+        <v>4.8095</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7993</v>
+        <v>2.4469</v>
       </c>
       <c r="G15" t="n">
-        <v>4.189</v>
+        <v>6.3387</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6479</v>
+        <v>3.0477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5411</v>
+        <v>3.2911</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0021</v>
+        <v>5.5484</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8155</v>
+        <v>3.0919</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1866</v>
+        <v>2.4565</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1869</v>
+        <v>0.7903</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8324</v>
+        <v>-0.0442</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3546</v>
+        <v>0.8345</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6668</v>
+        <v>0.4623</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8672</v>
+        <v>0.3992</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7996</v>
+        <v>0.0631</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.5766</v>
+        <v>5.1581</v>
       </c>
       <c r="E16" t="n">
-        <v>4.633</v>
+        <v>1.6098</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9436</v>
+        <v>3.5483</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3679</v>
+        <v>4.1891</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0548</v>
+        <v>3.6421</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3131</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>5.6068</v>
+        <v>2.9818</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1201</v>
+        <v>2.7956</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4867</v>
+        <v>0.1862</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7611</v>
+        <v>1.2073</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0653</v>
+        <v>0.8465</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8264</v>
+        <v>0.3608</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.245</v>
+        <v>1.8583</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1603</v>
+        <v>1.34</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4053</v>
+        <v>0.5184</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.5321</v>
+        <v>4.509</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5597</v>
+        <v>0.0388</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9724</v>
+        <v>4.4701</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2801</v>
+        <v>1.2382</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9335</v>
+        <v>2.7905</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3466</v>
+        <v>-1.5523</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3831</v>
+        <v>0.187</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2339</v>
+        <v>1.9305</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1493</v>
+        <v>-1.7436</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.103</v>
+        <v>1.0512</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3003</v>
+        <v>0.86</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1973</v>
+        <v>0.1912</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>2.5039</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>2.7316</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1593</v>
+        <v>1.3116</v>
       </c>
       <c r="T17" t="n">
-        <v>3.4449</v>
+        <v>0.4665</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2855</v>
+        <v>0.8451</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3992</v>
+        <v>2.9696</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2351</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>4.6343</v>
+        <v>3.6475</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2214</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7701</v>
+        <v>0.6713</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5487</v>
+        <v>-1.6345</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2121</v>
+        <v>-1.5535</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9395</v>
+        <v>0.2273</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.7274</v>
+        <v>-1.7808</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0094</v>
+        <v>0.5903</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8307</v>
+        <v>0.444</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1787</v>
+        <v>0.1463</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4952</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>2.722</v>
+        <v>2.5039</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2289</v>
+        <v>0.6156</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8347</v>
+        <v>0.0624</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0637</v>
+        <v>0.5532</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5463</v>
+        <v>2.1789</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3856</v>
+        <v>2.1789</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6677</v>
+        <v>2.6218</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4702</v>
+        <v>1.1876</v>
       </c>
       <c r="F19" t="n">
-        <v>3.1379</v>
+        <v>1.4343</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9683</v>
+        <v>2.2874</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6578000000000001</v>
+        <v>1.9357</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.626</v>
+        <v>0.3518</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5294</v>
+        <v>2.3725</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2353</v>
+        <v>2.2236</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.7647</v>
+        <v>0.1489</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5611</v>
+        <v>-0.0851</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4224</v>
+        <v>-0.2879</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1387</v>
+        <v>0.2028</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1342</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6835</v>
+        <v>1.2449</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7652</v>
+        <v>1.0914</v>
       </c>
       <c r="U19" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.1535</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. KEITA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1589</v>
+        <v>0.6995</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2953</v>
+        <v>-0.6339</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1364</v>
+        <v>1.3334</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0401</v>
+        <v>-0.5965</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4213</v>
+        <v>0.2264</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3812</v>
+        <v>-0.8229</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3648</v>
+        <v>-1.0145</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2322</v>
+        <v>-0.0452</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5971</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.405</v>
+        <v>0.4179</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1891</v>
+        <v>0.2716</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2159</v>
+        <v>0.1463</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>2.7316</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0278</v>
+        <v>0.0896</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0696</v>
+        <v>0.2715</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0417</v>
+        <v>-0.1819</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6892</v>
+        <v>0.674</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4152</v>
+        <v>-4.535</v>
       </c>
       <c r="F21" t="n">
-        <v>0.726</v>
+        <v>5.209</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.59</v>
+        <v>2.8259</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2177</v>
+        <v>1.1143</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8078</v>
+        <v>1.7116</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.978</v>
+        <v>0.9725</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0315</v>
+        <v>-0.0624</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9464</v>
+        <v>1.035</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3879</v>
+        <v>1.8534</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2493</v>
+        <v>1.1768</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1387</v>
+        <v>0.6766</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5878</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-5.9184</v>
       </c>
       <c r="R21" t="n">
-        <v>2.722</v>
+        <v>3.1868</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3014</v>
+        <v>0.5797</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5565</v>
+        <v>0.4109</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7449</v>
+        <v>0.1688</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>S. KEITA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7403</v>
+        <v>0.3374</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.3217</v>
+        <v>0.4065</v>
       </c>
       <c r="F22" t="n">
-        <v>4.5814</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>2.8252</v>
+        <v>-0.0435</v>
       </c>
       <c r="H22" t="n">
-        <v>1.114</v>
+        <v>-0.4249</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7113</v>
+        <v>0.3813</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9933</v>
+        <v>0.3577</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0488</v>
+        <v>-0.2381</v>
       </c>
       <c r="L22" t="n">
-        <v>1.0422</v>
+        <v>0.5958</v>
       </c>
       <c r="M22" t="n">
-        <v>1.8319</v>
+        <v>-0.4012</v>
       </c>
       <c r="N22" t="n">
-        <v>1.1628</v>
+        <v>-0.1868</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6691</v>
+        <v>-0.2144</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.722</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.8976</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.1757</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8435</v>
+        <v>0.1533</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4174</v>
+        <v>0.0487</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4262</v>
+        <v>0.1046</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9998</v>
+        <v>-0.9062</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.6473</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3582</v>
+        <v>-0.2589</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3681</v>
+        <v>0.3725</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0131</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3812</v>
+        <v>0.3813</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6317</v>
+        <v>0.6303</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2636</v>
+        <v>-0.2578</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2338</v>
+        <v>-0.1405</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8277</v>
+        <v>-1.6488</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.145</v>
+        <v>-2.035</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3173</v>
+        <v>0.3862</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9621</v>
+        <v>-0.9613</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0028</v>
+        <v>0.0056</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9649</v>
+        <v>-0.9668</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7144</v>
+        <v>-0.7179</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2477</v>
+        <v>-0.2433</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1851</v>
+        <v>-0.0046</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>27.242</v>
+        <v>29.61060000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>6.773300000000001</v>
+        <v>6.482099999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>20.4688</v>
+        <v>23.1286</v>
       </c>
       <c r="G25" t="n">
-        <v>20.5765</v>
+        <v>20.58069999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>15.9654</v>
+        <v>16.0094</v>
       </c>
       <c r="I25" t="n">
-        <v>4.6112</v>
+        <v>4.5714</v>
       </c>
       <c r="J25" t="n">
-        <v>16.634</v>
+        <v>16.403</v>
       </c>
       <c r="K25" t="n">
-        <v>13.7029</v>
+        <v>13.5775</v>
       </c>
       <c r="L25" t="n">
-        <v>2.9315</v>
+        <v>2.8255</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9425</v>
+        <v>4.177700000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>2.2627</v>
+        <v>2.432</v>
       </c>
       <c r="O25" t="n">
-        <v>1.6799</v>
+        <v>1.7458</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.134199999999999</v>
+        <v>-1.1383</v>
       </c>
       <c r="Q25" t="n">
-        <v>-19.2808</v>
+        <v>-19.3488</v>
       </c>
       <c r="R25" t="n">
-        <v>18.1466</v>
+        <v>18.2104</v>
       </c>
       <c r="S25" t="n">
-        <v>4.5215</v>
+        <v>6.8996</v>
       </c>
       <c r="T25" t="n">
-        <v>4.567</v>
+        <v>4.596500000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.04559999999999982</v>
+        <v>2.3031</v>
       </c>
       <c r="V25" t="n">
-        <v>3.2781</v>
+        <v>3.2684</v>
       </c>
       <c r="W25" t="n">
-        <v>4.8529</v>
+        <v>4.831099999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.5748</v>
+        <v>-1.5628</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104548_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104548_W10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-4.8312</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104548_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-1.5628</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
